--- a/MWMWM-AB-Board-BOM.xlsx
+++ b/MWMWM-AB-Board-BOM.xlsx
@@ -9,8 +9,6 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -198,16 +196,25 @@
     <t xml:space="preserve">BC847</t>
   </si>
   <si>
-    <t xml:space="preserve">R7,R8,R9,R10,R11,R12,R13,R14,R15,R16,R17,R18,R19,R20,R21,R22,R40,R50</t>
+    <t xml:space="preserve">R7,R15,R41,R44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2930202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resistor_SMD:R_0805_2012Metric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R8,R9,R10,R11,R12,R13,R14,R16,R17,R18,R19,R20,R21,R22,R40,R50</t>
   </si>
   <si>
     <t xml:space="preserve">C17414</t>
   </si>
   <si>
     <t xml:space="preserve">10k</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resistor_SMD:R_0805_2012Metric</t>
   </si>
   <si>
     <t xml:space="preserve">R23,R24,R25,R26,R27,R28,R29,R30,R31,R34,R35,R36,R37,R42,R43,R48,R49</t>
@@ -235,15 +242,6 @@
   </si>
   <si>
     <t xml:space="preserve">1k</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R41,R44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C2930202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47k</t>
   </si>
   <si>
     <t xml:space="preserve">R45,R46</t>
@@ -308,7 +306,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -361,6 +359,19 @@
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
@@ -467,7 +478,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -501,11 +512,19 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -524,23 +543,23 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -572,7 +591,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -659,9 +678,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>631080</xdr:colOff>
+      <xdr:colOff>630360</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>150840</xdr:rowOff>
+      <xdr:rowOff>150120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -675,7 +694,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9360" y="209520"/>
-          <a:ext cx="1256040" cy="370080"/>
+          <a:ext cx="1255320" cy="369360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1075,20 +1094,20 @@
       <c r="A7" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="0" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="7"/>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="0" t="s">
         <v>13</v>
       </c>
       <c r="H7" s="7"/>
@@ -1115,20 +1134,20 @@
       <c r="A8" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="8" t="n">
+      <c r="C8" s="0" t="n">
         <v>4</v>
       </c>
       <c r="D8" s="7"/>
       <c r="E8" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="0" t="s">
         <v>13</v>
       </c>
       <c r="H8" s="7"/>
@@ -1155,20 +1174,20 @@
       <c r="A9" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C9" s="0" t="n">
         <v>4</v>
       </c>
       <c r="D9" s="7"/>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="0" t="s">
         <v>13</v>
       </c>
       <c r="H9" s="7"/>
@@ -1195,18 +1214,18 @@
       <c r="A10" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="8" t="n">
+      <c r="C10" s="0" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="0" t="s">
         <v>22</v>
       </c>
       <c r="H10" s="7"/>
@@ -1235,18 +1254,18 @@
       <c r="A11" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="8" t="n">
+      <c r="C11" s="0" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="0" t="s">
         <v>26</v>
       </c>
       <c r="H11" s="7"/>
@@ -1275,20 +1294,20 @@
       <c r="A12" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="8" t="n">
+      <c r="C12" s="0" t="n">
         <v>16</v>
       </c>
       <c r="D12" s="7"/>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="0" t="s">
         <v>30</v>
       </c>
       <c r="H12" s="7"/>
@@ -1315,18 +1334,18 @@
       <c r="A13" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="8" t="n">
+      <c r="C13" s="0" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="G13" s="0" t="s">
         <v>33</v>
       </c>
       <c r="H13" s="7"/>
@@ -1355,18 +1374,18 @@
       <c r="A14" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="8" t="n">
+      <c r="C14" s="0" t="n">
         <v>4</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G14" s="0" t="s">
         <v>36</v>
       </c>
       <c r="H14" s="7"/>
@@ -1395,20 +1414,20 @@
       <c r="A15" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="8" t="n">
+      <c r="C15" s="0" t="n">
         <v>1</v>
       </c>
       <c r="D15" s="7"/>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H15" s="7"/>
@@ -1435,20 +1454,20 @@
       <c r="A16" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="8" t="n">
+      <c r="C16" s="0" t="n">
         <v>1</v>
       </c>
       <c r="D16" s="7"/>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="G16" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H16" s="7"/>
@@ -1475,20 +1494,20 @@
       <c r="A17" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="8" t="n">
-        <v>18</v>
+      <c r="C17" s="0" t="n">
+        <v>4</v>
       </c>
       <c r="D17" s="7"/>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="G17" s="0" t="s">
         <v>47</v>
       </c>
       <c r="H17" s="7"/>
@@ -1515,20 +1534,20 @@
       <c r="A18" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="0" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="8" t="n">
-        <v>17</v>
+      <c r="C18" s="0" t="n">
+        <v>16</v>
       </c>
       <c r="D18" s="7"/>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="G18" s="0" t="s">
         <v>47</v>
       </c>
       <c r="H18" s="7"/>
@@ -1555,20 +1574,20 @@
       <c r="A19" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="0" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="8" t="n">
-        <v>1</v>
+      <c r="C19" s="0" t="n">
+        <v>17</v>
       </c>
       <c r="D19" s="7"/>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="0" t="s">
         <v>53</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="G19" s="0" t="s">
         <v>47</v>
       </c>
       <c r="H19" s="7"/>
@@ -1595,20 +1614,20 @@
       <c r="A20" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="C20" s="8" t="n">
-        <v>3</v>
+      <c r="C20" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="D20" s="7"/>
-      <c r="E20" s="8" t="s">
+      <c r="E20" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F20" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="G20" s="0" t="s">
         <v>47</v>
       </c>
       <c r="H20" s="7"/>
@@ -1635,23 +1654,23 @@
       <c r="A21" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="0" t="s">
         <v>57</v>
       </c>
-      <c r="C21" s="8" t="n">
-        <v>2</v>
+      <c r="C21" s="0" t="n">
+        <v>3</v>
       </c>
-      <c r="D21" s="10"/>
-      <c r="E21" s="8" t="s">
+      <c r="D21" s="12"/>
+      <c r="E21" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="F21" s="0" t="s">
         <v>59</v>
       </c>
-      <c r="G21" s="8" t="s">
+      <c r="G21" s="0" t="s">
         <v>47</v>
       </c>
-      <c r="H21" s="10"/>
+      <c r="H21" s="12"/>
       <c r="I21" s="7"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
@@ -1675,24 +1694,24 @@
       <c r="A22" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="0" t="s">
         <v>60</v>
       </c>
-      <c r="C22" s="8" t="n">
+      <c r="C22" s="0" t="n">
         <v>2</v>
       </c>
       <c r="D22" s="7"/>
-      <c r="E22" s="8" t="s">
+      <c r="E22" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F22" s="0" t="s">
         <v>62</v>
       </c>
-      <c r="G22" s="8" t="s">
+      <c r="G22" s="0" t="s">
         <v>47</v>
       </c>
       <c r="H22" s="7"/>
-      <c r="I22" s="10"/>
+      <c r="I22" s="12"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
@@ -1715,41 +1734,41 @@
       <c r="A23" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="0" t="s">
         <v>63</v>
       </c>
-      <c r="C23" s="8" t="n">
+      <c r="C23" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="10"/>
-      <c r="E23" s="8" t="s">
+      <c r="D23" s="12"/>
+      <c r="E23" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="F23" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="G23" s="8" t="s">
+      <c r="G23" s="0" t="s">
         <v>47</v>
       </c>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="0" t="s">
         <v>66</v>
       </c>
-      <c r="C24" s="8" t="n">
+      <c r="C24" s="0" t="n">
         <v>3</v>
       </c>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="8" t="s">
-        <v>50</v>
+      <c r="F24" s="0" t="s">
+        <v>53</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="G24" s="0" t="s">
         <v>67</v>
       </c>
       <c r="H24" s="7"/>
@@ -1778,20 +1797,20 @@
       <c r="A25" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="C25" s="8" t="n">
+      <c r="C25" s="0" t="n">
         <v>3</v>
       </c>
       <c r="D25" s="7"/>
-      <c r="E25" s="8" t="s">
+      <c r="E25" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="F25" s="0" t="s">
         <v>70</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="G25" s="0" t="s">
         <v>71</v>
       </c>
       <c r="H25" s="7"/>
@@ -1818,20 +1837,20 @@
       <c r="A26" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="8" t="n">
+      <c r="C26" s="0" t="n">
         <v>1</v>
       </c>
       <c r="D26" s="7"/>
-      <c r="E26" s="9" t="s">
+      <c r="E26" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="F26" s="0" t="s">
         <v>74</v>
       </c>
-      <c r="G26" s="8" t="s">
+      <c r="G26" s="0" t="s">
         <v>75</v>
       </c>
       <c r="H26" s="7"/>
@@ -1855,43 +1874,43 @@
       <c r="Z26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="11"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
-      <c r="N27" s="15"/>
-      <c r="O27" s="15"/>
-      <c r="P27" s="15"/>
-      <c r="Q27" s="15"/>
-      <c r="R27" s="15"/>
-      <c r="S27" s="15"/>
-      <c r="T27" s="15"/>
-      <c r="U27" s="15"/>
-      <c r="V27" s="15"/>
-      <c r="W27" s="15"/>
-      <c r="X27" s="15"/>
-      <c r="Y27" s="15"/>
-      <c r="Z27" s="15"/>
+      <c r="A27" s="13"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="16"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="17"/>
+      <c r="N27" s="17"/>
+      <c r="O27" s="17"/>
+      <c r="P27" s="17"/>
+      <c r="Q27" s="17"/>
+      <c r="R27" s="17"/>
+      <c r="S27" s="17"/>
+      <c r="T27" s="17"/>
+      <c r="U27" s="17"/>
+      <c r="V27" s="17"/>
+      <c r="W27" s="17"/>
+      <c r="X27" s="17"/>
+      <c r="Y27" s="17"/>
+      <c r="Z27" s="17"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="11"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="14"/>
+      <c r="A28" s="13"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="16"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
@@ -1911,15 +1930,15 @@
       <c r="Z28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="11"/>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
+      <c r="A29" s="13"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
@@ -1939,15 +1958,15 @@
       <c r="Z29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="11"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
@@ -1967,15 +1986,15 @@
       <c r="Z30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="11"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
+      <c r="A31" s="13"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
@@ -2128,17 +2147,17 @@
       <c r="Z37" s="2"/>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="16" t="s">
+      <c r="A38" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="B38" s="16"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="16"/>
-      <c r="I38" s="16"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
@@ -2158,15 +2177,15 @@
       <c r="Z38" s="2"/>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="17"/>
-      <c r="B39" s="17"/>
-      <c r="C39" s="17"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="17"/>
-      <c r="G39" s="17"/>
-      <c r="H39" s="17"/>
-      <c r="I39" s="17"/>
+      <c r="A39" s="19"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
@@ -2186,17 +2205,17 @@
       <c r="Z39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="18" t="s">
+      <c r="A40" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="B40" s="18"/>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="18"/>
-      <c r="H40" s="18"/>
-      <c r="I40" s="18"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="20"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
@@ -2254,11 +2273,11 @@
       <c r="Z42" s="2"/>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="19"/>
-      <c r="B43" s="20"/>
-      <c r="G43" s="20"/>
-      <c r="H43" s="21"/>
-      <c r="I43" s="21"/>
+      <c r="A43" s="21"/>
+      <c r="B43" s="22"/>
+      <c r="G43" s="22"/>
+      <c r="H43" s="23"/>
+      <c r="I43" s="23"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
       <c r="L43" s="2"/>
@@ -2278,11 +2297,11 @@
       <c r="Z43" s="2"/>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="19"/>
-      <c r="B44" s="20"/>
-      <c r="G44" s="20"/>
-      <c r="H44" s="21"/>
-      <c r="I44" s="21"/>
+      <c r="A44" s="21"/>
+      <c r="B44" s="22"/>
+      <c r="G44" s="22"/>
+      <c r="H44" s="23"/>
+      <c r="I44" s="23"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
@@ -2302,11 +2321,11 @@
       <c r="Z44" s="2"/>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="19"/>
-      <c r="B45" s="20"/>
-      <c r="G45" s="20"/>
-      <c r="H45" s="21"/>
-      <c r="I45" s="21"/>
+      <c r="A45" s="21"/>
+      <c r="B45" s="22"/>
+      <c r="G45" s="22"/>
+      <c r="H45" s="23"/>
+      <c r="I45" s="23"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
       <c r="L45" s="2"/>
@@ -2326,11 +2345,11 @@
       <c r="Z45" s="2"/>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="19"/>
-      <c r="B46" s="20"/>
-      <c r="G46" s="20"/>
-      <c r="H46" s="21"/>
-      <c r="I46" s="21"/>
+      <c r="A46" s="21"/>
+      <c r="B46" s="22"/>
+      <c r="G46" s="22"/>
+      <c r="H46" s="23"/>
+      <c r="I46" s="23"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
@@ -2350,11 +2369,11 @@
       <c r="Z46" s="2"/>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="19"/>
-      <c r="B47" s="20"/>
-      <c r="G47" s="20"/>
-      <c r="H47" s="21"/>
-      <c r="I47" s="22"/>
+      <c r="A47" s="21"/>
+      <c r="B47" s="22"/>
+      <c r="G47" s="22"/>
+      <c r="H47" s="23"/>
+      <c r="I47" s="24"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
       <c r="L47" s="2"/>
@@ -2374,11 +2393,11 @@
       <c r="Z47" s="2"/>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="19"/>
-      <c r="B48" s="20"/>
-      <c r="G48" s="23"/>
-      <c r="H48" s="21"/>
-      <c r="I48" s="22"/>
+      <c r="A48" s="21"/>
+      <c r="B48" s="22"/>
+      <c r="G48" s="25"/>
+      <c r="H48" s="23"/>
+      <c r="I48" s="24"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
       <c r="L48" s="2"/>
@@ -2398,11 +2417,11 @@
       <c r="Z48" s="2"/>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="19"/>
-      <c r="B49" s="20"/>
-      <c r="G49" s="23"/>
-      <c r="H49" s="21"/>
-      <c r="I49" s="22"/>
+      <c r="A49" s="21"/>
+      <c r="B49" s="22"/>
+      <c r="G49" s="25"/>
+      <c r="H49" s="23"/>
+      <c r="I49" s="24"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
       <c r="L49" s="2"/>
@@ -2422,11 +2441,11 @@
       <c r="Z49" s="2"/>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="19"/>
-      <c r="B50" s="20"/>
-      <c r="G50" s="23"/>
-      <c r="H50" s="21"/>
-      <c r="I50" s="22"/>
+      <c r="A50" s="21"/>
+      <c r="B50" s="22"/>
+      <c r="G50" s="25"/>
+      <c r="H50" s="23"/>
+      <c r="I50" s="24"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
       <c r="L50" s="2"/>
@@ -2446,11 +2465,11 @@
       <c r="Z50" s="2"/>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="19"/>
-      <c r="B51" s="20"/>
-      <c r="G51" s="23"/>
-      <c r="H51" s="21"/>
-      <c r="I51" s="21"/>
+      <c r="A51" s="21"/>
+      <c r="B51" s="22"/>
+      <c r="G51" s="25"/>
+      <c r="H51" s="23"/>
+      <c r="I51" s="23"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
       <c r="L51" s="2"/>
@@ -2470,11 +2489,11 @@
       <c r="Z51" s="2"/>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="19"/>
-      <c r="B52" s="20"/>
-      <c r="G52" s="23"/>
-      <c r="H52" s="21"/>
-      <c r="I52" s="21"/>
+      <c r="A52" s="21"/>
+      <c r="B52" s="22"/>
+      <c r="G52" s="25"/>
+      <c r="H52" s="23"/>
+      <c r="I52" s="23"/>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
@@ -2494,11 +2513,11 @@
       <c r="Z52" s="2"/>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="19"/>
-      <c r="B53" s="20"/>
-      <c r="G53" s="23"/>
-      <c r="H53" s="21"/>
-      <c r="I53" s="21"/>
+      <c r="A53" s="21"/>
+      <c r="B53" s="22"/>
+      <c r="G53" s="25"/>
+      <c r="H53" s="23"/>
+      <c r="I53" s="23"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
@@ -2518,11 +2537,11 @@
       <c r="Z53" s="2"/>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="19"/>
-      <c r="B54" s="20"/>
-      <c r="G54" s="23"/>
-      <c r="H54" s="21"/>
-      <c r="I54" s="21"/>
+      <c r="A54" s="21"/>
+      <c r="B54" s="22"/>
+      <c r="G54" s="25"/>
+      <c r="H54" s="23"/>
+      <c r="I54" s="23"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
@@ -2542,11 +2561,11 @@
       <c r="Z54" s="2"/>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="19"/>
-      <c r="B55" s="20"/>
-      <c r="G55" s="23"/>
-      <c r="H55" s="21"/>
-      <c r="I55" s="21"/>
+      <c r="A55" s="21"/>
+      <c r="B55" s="22"/>
+      <c r="G55" s="25"/>
+      <c r="H55" s="23"/>
+      <c r="I55" s="23"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
       <c r="L55" s="2"/>
@@ -2566,11 +2585,11 @@
       <c r="Z55" s="2"/>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="19"/>
-      <c r="B56" s="20"/>
-      <c r="G56" s="23"/>
-      <c r="H56" s="21"/>
-      <c r="I56" s="21"/>
+      <c r="A56" s="21"/>
+      <c r="B56" s="22"/>
+      <c r="G56" s="25"/>
+      <c r="H56" s="23"/>
+      <c r="I56" s="23"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
       <c r="L56" s="2"/>
@@ -2590,11 +2609,11 @@
       <c r="Z56" s="2"/>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="19"/>
-      <c r="B57" s="20"/>
-      <c r="G57" s="23"/>
-      <c r="H57" s="21"/>
-      <c r="I57" s="21"/>
+      <c r="A57" s="21"/>
+      <c r="B57" s="22"/>
+      <c r="G57" s="25"/>
+      <c r="H57" s="23"/>
+      <c r="I57" s="23"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
       <c r="L57" s="2"/>
@@ -2614,11 +2633,11 @@
       <c r="Z57" s="2"/>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="19"/>
-      <c r="B58" s="20"/>
-      <c r="G58" s="20"/>
-      <c r="H58" s="20"/>
-      <c r="I58" s="22"/>
+      <c r="A58" s="21"/>
+      <c r="B58" s="22"/>
+      <c r="G58" s="22"/>
+      <c r="H58" s="22"/>
+      <c r="I58" s="24"/>
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
       <c r="L58" s="2"/>
@@ -2638,11 +2657,11 @@
       <c r="Z58" s="2"/>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="19"/>
-      <c r="B59" s="20"/>
-      <c r="G59" s="20"/>
-      <c r="H59" s="20"/>
-      <c r="I59" s="20"/>
+      <c r="A59" s="21"/>
+      <c r="B59" s="22"/>
+      <c r="G59" s="22"/>
+      <c r="H59" s="22"/>
+      <c r="I59" s="22"/>
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
       <c r="L59" s="2"/>
@@ -2662,11 +2681,11 @@
       <c r="Z59" s="2"/>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="19"/>
-      <c r="B60" s="20"/>
-      <c r="G60" s="20"/>
-      <c r="H60" s="20"/>
-      <c r="I60" s="22"/>
+      <c r="A60" s="21"/>
+      <c r="B60" s="22"/>
+      <c r="G60" s="22"/>
+      <c r="H60" s="22"/>
+      <c r="I60" s="24"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
       <c r="L60" s="2"/>
@@ -2686,11 +2705,11 @@
       <c r="Z60" s="2"/>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="19"/>
-      <c r="B61" s="20"/>
-      <c r="G61" s="20"/>
-      <c r="H61" s="20"/>
-      <c r="I61" s="20"/>
+      <c r="A61" s="21"/>
+      <c r="B61" s="22"/>
+      <c r="G61" s="22"/>
+      <c r="H61" s="22"/>
+      <c r="I61" s="22"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
       <c r="L61" s="2"/>
@@ -2710,15 +2729,15 @@
       <c r="Z61" s="2"/>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="19"/>
-      <c r="B62" s="20"/>
-      <c r="C62" s="24"/>
-      <c r="D62" s="20"/>
-      <c r="E62" s="20"/>
-      <c r="F62" s="20"/>
-      <c r="G62" s="20"/>
-      <c r="H62" s="20"/>
-      <c r="I62" s="22"/>
+      <c r="A62" s="21"/>
+      <c r="B62" s="22"/>
+      <c r="C62" s="26"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="22"/>
+      <c r="F62" s="22"/>
+      <c r="G62" s="22"/>
+      <c r="H62" s="22"/>
+      <c r="I62" s="24"/>
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
       <c r="L62" s="2"/>
@@ -2794,12 +2813,12 @@
       <c r="Z64" s="2"/>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="20"/>
-      <c r="B65" s="20"/>
-      <c r="C65" s="20"/>
-      <c r="E65" s="20"/>
-      <c r="F65" s="20"/>
-      <c r="G65" s="20"/>
+      <c r="A65" s="22"/>
+      <c r="B65" s="22"/>
+      <c r="C65" s="22"/>
+      <c r="E65" s="22"/>
+      <c r="F65" s="22"/>
+      <c r="G65" s="22"/>
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
       <c r="L65" s="2"/>
@@ -2819,12 +2838,12 @@
       <c r="Z65" s="2"/>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="20"/>
-      <c r="B66" s="20"/>
-      <c r="C66" s="20"/>
-      <c r="E66" s="25"/>
-      <c r="F66" s="20"/>
-      <c r="G66" s="20"/>
+      <c r="A66" s="22"/>
+      <c r="B66" s="22"/>
+      <c r="C66" s="22"/>
+      <c r="E66" s="27"/>
+      <c r="F66" s="22"/>
+      <c r="G66" s="22"/>
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
       <c r="L66" s="2"/>
@@ -2844,12 +2863,12 @@
       <c r="Z66" s="2"/>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="20"/>
-      <c r="B67" s="20"/>
-      <c r="C67" s="20"/>
-      <c r="F67" s="20"/>
-      <c r="G67" s="20"/>
-      <c r="I67" s="20"/>
+      <c r="A67" s="22"/>
+      <c r="B67" s="22"/>
+      <c r="C67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="I67" s="22"/>
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
       <c r="L67" s="2"/>
@@ -2869,12 +2888,12 @@
       <c r="Z67" s="2"/>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="20"/>
-      <c r="B68" s="20"/>
-      <c r="C68" s="20"/>
-      <c r="F68" s="20"/>
-      <c r="G68" s="20"/>
-      <c r="I68" s="20"/>
+      <c r="A68" s="22"/>
+      <c r="B68" s="22"/>
+      <c r="C68" s="22"/>
+      <c r="F68" s="22"/>
+      <c r="G68" s="22"/>
+      <c r="I68" s="22"/>
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
       <c r="L68" s="2"/>
@@ -2894,12 +2913,12 @@
       <c r="Z68" s="2"/>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="20"/>
-      <c r="B69" s="20"/>
-      <c r="C69" s="20"/>
-      <c r="E69" s="25"/>
-      <c r="F69" s="20"/>
-      <c r="G69" s="20"/>
+      <c r="A69" s="22"/>
+      <c r="B69" s="22"/>
+      <c r="C69" s="22"/>
+      <c r="E69" s="27"/>
+      <c r="F69" s="22"/>
+      <c r="G69" s="22"/>
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
       <c r="L69" s="2"/>
@@ -2919,12 +2938,12 @@
       <c r="Z69" s="2"/>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="20"/>
-      <c r="B70" s="20"/>
-      <c r="C70" s="20"/>
-      <c r="E70" s="20"/>
-      <c r="F70" s="20"/>
-      <c r="G70" s="20"/>
+      <c r="A70" s="22"/>
+      <c r="B70" s="22"/>
+      <c r="C70" s="22"/>
+      <c r="E70" s="22"/>
+      <c r="F70" s="22"/>
+      <c r="G70" s="22"/>
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
       <c r="L70" s="2"/>
@@ -2944,12 +2963,12 @@
       <c r="Z70" s="2"/>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="20"/>
-      <c r="B71" s="20"/>
-      <c r="C71" s="20"/>
-      <c r="E71" s="20"/>
-      <c r="F71" s="20"/>
-      <c r="G71" s="20"/>
+      <c r="A71" s="22"/>
+      <c r="B71" s="22"/>
+      <c r="C71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
       <c r="L71" s="2"/>
@@ -2969,12 +2988,12 @@
       <c r="Z71" s="2"/>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="20"/>
-      <c r="B72" s="20"/>
-      <c r="C72" s="20"/>
-      <c r="E72" s="25"/>
-      <c r="F72" s="20"/>
-      <c r="G72" s="20"/>
+      <c r="A72" s="22"/>
+      <c r="B72" s="22"/>
+      <c r="C72" s="22"/>
+      <c r="E72" s="27"/>
+      <c r="F72" s="22"/>
+      <c r="G72" s="22"/>
       <c r="J72" s="2"/>
       <c r="K72" s="2"/>
       <c r="L72" s="2"/>
@@ -2994,12 +3013,12 @@
       <c r="Z72" s="2"/>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="20"/>
-      <c r="B73" s="20"/>
-      <c r="C73" s="20"/>
-      <c r="E73" s="20"/>
-      <c r="F73" s="20"/>
-      <c r="G73" s="20"/>
+      <c r="A73" s="22"/>
+      <c r="B73" s="22"/>
+      <c r="C73" s="22"/>
+      <c r="E73" s="22"/>
+      <c r="F73" s="22"/>
+      <c r="G73" s="22"/>
       <c r="J73" s="2"/>
       <c r="K73" s="2"/>
       <c r="L73" s="2"/>
@@ -3019,12 +3038,12 @@
       <c r="Z73" s="2"/>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="20"/>
-      <c r="B74" s="20"/>
-      <c r="C74" s="20"/>
-      <c r="E74" s="20"/>
-      <c r="F74" s="20"/>
-      <c r="G74" s="20"/>
+      <c r="A74" s="22"/>
+      <c r="B74" s="22"/>
+      <c r="C74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="F74" s="22"/>
+      <c r="G74" s="22"/>
       <c r="J74" s="2"/>
       <c r="K74" s="2"/>
       <c r="L74" s="2"/>
@@ -3044,12 +3063,12 @@
       <c r="Z74" s="2"/>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="20"/>
-      <c r="B75" s="20"/>
-      <c r="C75" s="20"/>
-      <c r="F75" s="20"/>
-      <c r="G75" s="20"/>
-      <c r="I75" s="20"/>
+      <c r="A75" s="22"/>
+      <c r="B75" s="22"/>
+      <c r="C75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="I75" s="22"/>
       <c r="J75" s="2"/>
       <c r="K75" s="2"/>
       <c r="L75" s="2"/>
@@ -3069,12 +3088,12 @@
       <c r="Z75" s="2"/>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="20"/>
-      <c r="B76" s="20"/>
-      <c r="C76" s="20"/>
+      <c r="A76" s="22"/>
+      <c r="B76" s="22"/>
+      <c r="C76" s="22"/>
       <c r="E76" s="2"/>
-      <c r="F76" s="20"/>
-      <c r="G76" s="20"/>
+      <c r="F76" s="22"/>
+      <c r="G76" s="22"/>
       <c r="J76" s="2"/>
       <c r="K76" s="2"/>
       <c r="L76" s="2"/>
@@ -3094,12 +3113,12 @@
       <c r="Z76" s="2"/>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="20"/>
-      <c r="B77" s="20"/>
-      <c r="C77" s="20"/>
-      <c r="E77" s="20"/>
-      <c r="F77" s="20"/>
-      <c r="G77" s="20"/>
+      <c r="A77" s="22"/>
+      <c r="B77" s="22"/>
+      <c r="C77" s="22"/>
+      <c r="E77" s="22"/>
+      <c r="F77" s="22"/>
+      <c r="G77" s="22"/>
       <c r="J77" s="2"/>
       <c r="K77" s="2"/>
       <c r="L77" s="2"/>
@@ -3119,12 +3138,12 @@
       <c r="Z77" s="2"/>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="20"/>
-      <c r="B78" s="20"/>
-      <c r="C78" s="20"/>
-      <c r="E78" s="26"/>
-      <c r="F78" s="20"/>
-      <c r="G78" s="20"/>
+      <c r="A78" s="22"/>
+      <c r="B78" s="22"/>
+      <c r="C78" s="22"/>
+      <c r="E78" s="28"/>
+      <c r="F78" s="22"/>
+      <c r="G78" s="22"/>
       <c r="J78" s="2"/>
       <c r="K78" s="2"/>
       <c r="L78" s="2"/>
@@ -28979,2048 +28998,4 @@
   </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="14.43359375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="1" style="1" width="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="62" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="63" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="64" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="65" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="66" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="67" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="68" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="69" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="70" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="71" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="72" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="73" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="74" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="75" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="76" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="77" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="78" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="79" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="80" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="81" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="82" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="83" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="84" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="85" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="86" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="87" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="88" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="89" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="90" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="91" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="92" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="93" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="94" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="95" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="96" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="97" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="98" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="99" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="100" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="101" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="102" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="103" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="104" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="105" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="106" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="107" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="108" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="109" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="110" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="111" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="112" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="113" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="114" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="115" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="116" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="117" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="118" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="119" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="120" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="121" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="122" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="123" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="124" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="125" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="126" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="127" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="128" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="129" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="130" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="131" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="132" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="133" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="134" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="135" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="136" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="137" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="138" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="139" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="140" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="141" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="142" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="143" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="144" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="145" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="146" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="147" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="148" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="149" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="150" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="151" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="152" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="153" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="154" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="155" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="156" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="157" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="158" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="159" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="160" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="161" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="162" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="163" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="164" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="165" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="166" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="167" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="168" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="169" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="170" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="171" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="172" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="173" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="174" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="175" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="176" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="177" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="178" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="179" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="180" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="181" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="182" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="183" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="184" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="185" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="186" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="187" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="188" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="189" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="190" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="191" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="192" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="193" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="194" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="195" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="196" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="197" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="198" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="199" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="200" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="201" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="202" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="203" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="204" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="205" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="206" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="207" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="208" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="209" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="210" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="211" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="212" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="213" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="214" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="215" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="216" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="217" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="218" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="219" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="220" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="221" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="222" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="223" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="224" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="225" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="226" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="227" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="228" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="229" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="230" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="231" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="232" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="233" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="234" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="235" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="236" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="237" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="238" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="239" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="240" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="241" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="242" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="243" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="244" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="245" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="246" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="247" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="248" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="249" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="250" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="251" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="252" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="253" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="254" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="255" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="256" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="257" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="258" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="259" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="260" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="261" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="262" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="263" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="264" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="265" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="266" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="267" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="268" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="269" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="270" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="271" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="272" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="273" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="274" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="275" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="276" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="277" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="278" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="279" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="280" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="281" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="282" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="283" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="284" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="285" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="286" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="287" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="288" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="289" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="290" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="291" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="292" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="293" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="294" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="295" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="296" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="297" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="298" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="299" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="300" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="301" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="302" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="303" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="304" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="305" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="306" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="307" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="308" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="309" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="310" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="311" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="312" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="313" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="314" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="315" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="316" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="317" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="318" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="319" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="320" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="321" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="322" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="323" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="324" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="325" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="326" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="327" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="328" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="329" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="330" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="331" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="332" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="333" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="334" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="335" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="336" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="337" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="338" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="339" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="340" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="341" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="342" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="343" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="344" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="345" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="346" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="347" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="348" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="349" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="350" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="351" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="352" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="353" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="354" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="355" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="356" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="357" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="358" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="359" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="360" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="361" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="362" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="363" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="364" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="365" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="366" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="367" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="368" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="369" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="370" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="371" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="372" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="373" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="374" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="375" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="376" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="377" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="378" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="379" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="380" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="381" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="382" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="383" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="384" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="385" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="386" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="387" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="388" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="389" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="390" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="391" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="392" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="393" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="394" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="395" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="396" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="397" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="398" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="399" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="400" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="401" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="402" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="403" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="404" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="405" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="406" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="407" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="408" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="409" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="410" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="411" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="412" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="413" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="414" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="415" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="416" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="417" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="418" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="419" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="420" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="421" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="422" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="423" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="424" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="425" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="426" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="427" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="428" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="429" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="430" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="431" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="432" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="433" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="434" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="435" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="436" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="437" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="438" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="439" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="440" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="441" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="442" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="443" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="444" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="445" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="446" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="447" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="448" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="449" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="450" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="451" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="452" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="453" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="454" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="455" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="456" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="457" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="458" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="459" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="460" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="461" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="462" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="463" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="464" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="465" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="466" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="467" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="468" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="469" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="470" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="471" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="472" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="473" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="474" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="475" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="476" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="477" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="478" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="479" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="480" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="481" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="482" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="483" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="484" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="485" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="486" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="487" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="488" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="489" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="490" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="491" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="492" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="493" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="494" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="495" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="496" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="497" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="498" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="499" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="500" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="501" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="502" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="503" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="504" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="505" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="506" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="507" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="508" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="509" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="510" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="511" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="512" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="513" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="514" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="515" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="516" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="517" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="518" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="519" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="520" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="521" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="522" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="523" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="524" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="525" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="526" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="527" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="528" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="529" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="530" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="531" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="532" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="533" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="534" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="535" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="536" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="537" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="538" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="539" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="540" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="541" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="542" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="543" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="544" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="545" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="546" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="547" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="548" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="549" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="550" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="551" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="552" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="553" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="554" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="555" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="556" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="557" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="558" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="559" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="560" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="561" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="562" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="563" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="564" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="565" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="566" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="567" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="568" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="569" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="570" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="571" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="572" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="573" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="574" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="575" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="576" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="577" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="578" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="579" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="580" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="581" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="582" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="583" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="584" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="585" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="586" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="587" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="588" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="589" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="590" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="591" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="592" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="593" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="594" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="595" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="596" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="597" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="598" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="599" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="600" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="601" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="602" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="603" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="604" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="605" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="606" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="607" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="608" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="609" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="610" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="611" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="612" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="613" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="614" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="615" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="616" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="617" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="618" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="619" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="620" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="621" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="622" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="623" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="624" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="625" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="626" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="627" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="628" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="629" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="630" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="631" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="632" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="633" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="634" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="635" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="636" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="637" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="638" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="639" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="640" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="641" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="642" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="643" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="644" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="645" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="646" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="647" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="648" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="649" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="650" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="651" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="652" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="653" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="654" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="655" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="656" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="657" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="658" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="659" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="660" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="661" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="662" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="663" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="664" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="665" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="666" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="667" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="668" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="669" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="670" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="671" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="672" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="673" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="674" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="675" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="676" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="677" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="678" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="679" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="680" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="681" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="682" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="683" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="684" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="685" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="686" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="687" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="688" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="689" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="690" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="691" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="692" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="693" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="694" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="695" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="696" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="697" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="698" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="699" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="700" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="701" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="702" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="703" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="704" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="705" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="706" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="707" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="708" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="709" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="710" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="711" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="712" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="713" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="714" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="715" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="716" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="717" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="718" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="719" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="720" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="721" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="722" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="723" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="724" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="725" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="726" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="727" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="728" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="729" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="730" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="731" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="732" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="733" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="734" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="735" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="736" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="737" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="738" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="739" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="740" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="741" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="742" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="743" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="744" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="745" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="746" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="747" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="748" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="749" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="750" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="751" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="752" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="753" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="754" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="755" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="756" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="757" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="758" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="759" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="760" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="761" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="762" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="763" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="764" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="765" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="766" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="767" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="768" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="769" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="770" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="771" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="772" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="773" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="774" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="775" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="776" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="777" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="778" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="779" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="780" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="781" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="782" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="783" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="784" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="785" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="786" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="787" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="788" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="789" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="790" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="791" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="792" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="793" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="794" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="795" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="796" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="797" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="798" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="799" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="800" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="801" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="802" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="803" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="804" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="805" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="806" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="807" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="808" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="809" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="810" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="811" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="812" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="813" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="814" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="815" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="816" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="817" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="818" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="819" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="820" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="821" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="822" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="823" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="824" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="825" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="826" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="827" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="828" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="829" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="830" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="831" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="832" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="833" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="834" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="835" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="836" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="837" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="838" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="839" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="840" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="841" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="842" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="843" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="844" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="845" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="846" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="847" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="848" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="849" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="850" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="851" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="852" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="853" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="854" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="855" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="856" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="857" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="858" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="859" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="860" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="861" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="862" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="863" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="864" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="865" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="866" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="867" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="868" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="869" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="870" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="871" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="872" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="873" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="874" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="875" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="876" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="877" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="878" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="879" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="880" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="881" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="882" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="883" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="884" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="885" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="886" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="887" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="888" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="889" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="890" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="891" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="892" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="893" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="894" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="895" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="896" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="897" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="898" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="899" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="900" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="901" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="902" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="903" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="904" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="905" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="906" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="907" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="908" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="909" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="910" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="911" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="912" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="913" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="914" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="915" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="916" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="917" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="918" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="919" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="920" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="921" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="922" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="923" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="924" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="925" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="926" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="927" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="928" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="929" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="930" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="931" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="932" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="933" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="934" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="935" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="936" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="937" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="938" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="939" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="940" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="941" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="942" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="943" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="944" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="945" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="946" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="947" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="948" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="949" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="950" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="951" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="952" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="953" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="954" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="955" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="956" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="957" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="958" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="959" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="960" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="961" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="962" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="963" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="964" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="965" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="966" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="967" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="968" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="969" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="970" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="971" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="972" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="973" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="974" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="975" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="976" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="977" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="978" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="979" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="980" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="981" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="982" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="983" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="984" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="985" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="986" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="987" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="988" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="989" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="990" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="991" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="992" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="993" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="994" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="995" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="996" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="997" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="998" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="999" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1000" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="14.43359375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="1" style="1" width="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="62" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="63" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="64" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="65" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="66" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="67" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="68" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="69" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="70" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="71" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="72" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="73" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="74" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="75" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="76" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="77" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="78" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="79" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="80" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="81" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="82" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="83" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="84" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="85" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="86" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="87" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="88" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="89" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="90" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="91" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="92" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="93" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="94" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="95" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="96" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="97" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="98" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="99" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="100" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="101" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="102" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="103" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="104" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="105" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="106" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="107" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="108" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="109" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="110" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="111" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="112" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="113" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="114" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="115" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="116" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="117" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="118" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="119" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="120" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="121" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="122" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="123" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="124" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="125" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="126" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="127" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="128" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="129" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="130" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="131" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="132" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="133" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="134" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="135" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="136" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="137" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="138" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="139" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="140" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="141" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="142" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="143" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="144" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="145" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="146" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="147" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="148" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="149" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="150" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="151" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="152" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="153" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="154" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="155" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="156" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="157" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="158" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="159" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="160" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="161" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="162" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="163" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="164" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="165" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="166" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="167" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="168" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="169" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="170" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="171" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="172" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="173" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="174" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="175" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="176" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="177" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="178" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="179" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="180" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="181" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="182" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="183" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="184" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="185" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="186" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="187" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="188" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="189" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="190" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="191" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="192" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="193" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="194" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="195" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="196" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="197" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="198" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="199" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="200" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="201" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="202" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="203" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="204" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="205" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="206" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="207" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="208" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="209" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="210" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="211" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="212" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="213" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="214" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="215" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="216" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="217" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="218" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="219" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="220" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="221" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="222" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="223" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="224" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="225" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="226" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="227" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="228" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="229" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="230" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="231" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="232" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="233" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="234" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="235" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="236" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="237" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="238" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="239" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="240" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="241" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="242" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="243" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="244" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="245" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="246" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="247" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="248" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="249" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="250" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="251" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="252" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="253" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="254" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="255" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="256" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="257" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="258" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="259" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="260" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="261" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="262" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="263" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="264" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="265" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="266" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="267" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="268" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="269" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="270" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="271" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="272" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="273" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="274" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="275" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="276" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="277" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="278" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="279" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="280" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="281" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="282" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="283" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="284" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="285" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="286" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="287" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="288" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="289" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="290" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="291" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="292" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="293" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="294" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="295" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="296" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="297" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="298" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="299" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="300" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="301" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="302" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="303" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="304" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="305" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="306" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="307" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="308" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="309" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="310" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="311" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="312" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="313" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="314" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="315" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="316" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="317" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="318" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="319" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="320" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="321" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="322" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="323" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="324" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="325" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="326" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="327" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="328" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="329" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="330" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="331" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="332" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="333" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="334" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="335" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="336" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="337" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="338" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="339" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="340" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="341" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="342" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="343" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="344" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="345" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="346" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="347" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="348" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="349" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="350" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="351" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="352" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="353" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="354" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="355" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="356" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="357" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="358" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="359" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="360" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="361" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="362" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="363" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="364" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="365" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="366" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="367" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="368" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="369" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="370" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="371" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="372" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="373" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="374" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="375" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="376" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="377" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="378" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="379" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="380" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="381" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="382" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="383" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="384" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="385" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="386" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="387" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="388" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="389" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="390" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="391" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="392" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="393" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="394" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="395" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="396" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="397" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="398" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="399" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="400" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="401" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="402" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="403" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="404" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="405" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="406" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="407" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="408" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="409" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="410" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="411" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="412" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="413" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="414" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="415" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="416" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="417" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="418" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="419" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="420" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="421" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="422" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="423" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="424" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="425" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="426" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="427" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="428" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="429" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="430" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="431" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="432" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="433" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="434" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="435" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="436" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="437" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="438" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="439" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="440" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="441" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="442" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="443" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="444" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="445" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="446" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="447" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="448" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="449" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="450" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="451" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="452" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="453" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="454" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="455" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="456" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="457" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="458" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="459" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="460" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="461" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="462" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="463" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="464" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="465" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="466" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="467" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="468" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="469" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="470" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="471" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="472" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="473" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="474" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="475" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="476" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="477" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="478" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="479" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="480" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="481" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="482" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="483" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="484" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="485" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="486" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="487" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="488" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="489" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="490" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="491" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="492" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="493" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="494" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="495" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="496" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="497" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="498" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="499" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="500" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="501" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="502" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="503" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="504" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="505" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="506" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="507" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="508" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="509" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="510" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="511" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="512" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="513" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="514" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="515" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="516" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="517" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="518" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="519" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="520" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="521" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="522" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="523" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="524" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="525" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="526" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="527" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="528" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="529" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="530" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="531" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="532" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="533" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="534" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="535" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="536" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="537" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="538" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="539" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="540" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="541" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="542" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="543" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="544" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="545" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="546" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="547" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="548" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="549" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="550" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="551" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="552" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="553" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="554" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="555" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="556" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="557" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="558" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="559" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="560" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="561" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="562" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="563" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="564" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="565" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="566" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="567" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="568" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="569" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="570" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="571" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="572" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="573" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="574" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="575" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="576" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="577" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="578" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="579" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="580" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="581" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="582" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="583" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="584" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="585" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="586" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="587" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="588" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="589" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="590" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="591" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="592" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="593" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="594" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="595" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="596" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="597" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="598" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="599" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="600" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="601" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="602" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="603" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="604" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="605" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="606" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="607" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="608" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="609" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="610" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="611" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="612" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="613" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="614" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="615" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="616" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="617" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="618" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="619" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="620" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="621" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="622" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="623" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="624" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="625" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="626" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="627" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="628" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="629" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="630" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="631" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="632" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="633" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="634" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="635" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="636" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="637" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="638" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="639" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="640" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="641" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="642" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="643" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="644" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="645" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="646" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="647" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="648" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="649" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="650" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="651" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="652" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="653" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="654" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="655" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="656" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="657" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="658" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="659" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="660" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="661" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="662" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="663" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="664" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="665" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="666" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="667" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="668" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="669" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="670" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="671" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="672" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="673" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="674" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="675" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="676" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="677" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="678" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="679" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="680" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="681" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="682" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="683" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="684" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="685" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="686" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="687" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="688" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="689" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="690" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="691" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="692" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="693" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="694" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="695" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="696" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="697" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="698" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="699" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="700" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="701" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="702" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="703" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="704" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="705" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="706" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="707" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="708" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="709" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="710" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="711" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="712" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="713" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="714" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="715" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="716" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="717" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="718" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="719" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="720" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="721" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="722" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="723" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="724" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="725" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="726" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="727" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="728" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="729" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="730" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="731" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="732" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="733" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="734" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="735" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="736" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="737" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="738" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="739" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="740" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="741" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="742" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="743" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="744" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="745" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="746" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="747" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="748" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="749" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="750" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="751" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="752" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="753" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="754" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="755" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="756" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="757" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="758" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="759" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="760" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="761" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="762" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="763" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="764" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="765" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="766" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="767" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="768" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="769" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="770" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="771" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="772" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="773" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="774" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="775" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="776" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="777" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="778" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="779" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="780" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="781" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="782" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="783" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="784" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="785" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="786" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="787" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="788" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="789" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="790" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="791" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="792" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="793" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="794" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="795" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="796" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="797" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="798" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="799" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="800" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="801" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="802" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="803" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="804" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="805" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="806" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="807" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="808" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="809" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="810" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="811" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="812" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="813" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="814" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="815" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="816" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="817" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="818" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="819" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="820" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="821" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="822" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="823" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="824" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="825" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="826" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="827" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="828" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="829" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="830" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="831" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="832" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="833" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="834" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="835" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="836" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="837" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="838" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="839" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="840" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="841" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="842" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="843" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="844" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="845" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="846" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="847" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="848" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="849" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="850" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="851" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="852" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="853" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="854" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="855" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="856" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="857" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="858" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="859" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="860" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="861" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="862" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="863" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="864" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="865" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="866" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="867" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="868" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="869" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="870" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="871" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="872" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="873" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="874" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="875" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="876" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="877" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="878" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="879" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="880" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="881" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="882" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="883" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="884" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="885" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="886" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="887" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="888" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="889" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="890" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="891" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="892" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="893" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="894" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="895" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="896" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="897" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="898" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="899" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="900" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="901" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="902" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="903" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="904" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="905" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="906" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="907" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="908" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="909" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="910" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="911" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="912" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="913" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="914" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="915" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="916" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="917" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="918" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="919" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="920" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="921" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="922" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="923" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="924" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="925" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="926" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="927" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="928" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="929" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="930" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="931" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="932" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="933" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="934" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="935" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="936" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="937" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="938" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="939" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="940" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="941" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="942" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="943" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="944" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="945" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="946" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="947" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="948" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="949" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="950" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="951" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="952" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="953" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="954" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="955" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="956" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="957" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="958" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="959" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="960" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="961" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="962" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="963" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="964" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="965" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="966" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="967" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="968" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="969" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="970" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="971" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="972" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="973" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="974" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="975" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="976" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="977" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="978" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="979" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="980" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="981" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="982" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="983" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="984" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="985" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="986" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="987" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="988" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="989" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="990" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="991" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="992" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="993" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="994" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="995" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="996" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="997" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="998" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="999" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1000" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
 </file>